--- a/reports/FP_Assets_Details_2026.xlsx
+++ b/reports/FP_Assets_Details_2026.xlsx
@@ -12,7 +12,16 @@
     <sheet name="FP Common Area Bins" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="FP Staff Washroom" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'FP Planters'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FP Planters'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FP Planter Photos'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'FP Planter Photos'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'FP Common Area Bins'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'FP Common Area Bins'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'FP Staff Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FP Staff Washroom'!$A$1:$I$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -159,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -177,15 +186,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,8 +310,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -338,8 +338,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -366,8 +366,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -680,7 +680,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -968,6 +968,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -976,71 +977,96 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.45" customWidth="1" min="1" max="1"/>
     <col width="26.45" customWidth="1" min="2" max="2"/>
     <col width="22.45" customWidth="1" min="3" max="3"/>
+    <col width="24.45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="37.4" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Source sheet</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Shown at</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="115" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>cell B4</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="115" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>cell B19</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="115" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="115" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>cell B20</t>
         </is>
       </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1049,7 +1075,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1099,7 +1125,7 @@
       <c r="A3" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B3" s="12" t="n"/>
+      <c r="B3" s="9" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Fashion Lobby</t>
@@ -1119,6 +1145,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1126,7 +1153,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1143,47 +1170,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="55.4" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Washroom no</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Urinal</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Cubicle</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Pedal Bins </t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Toilet Roll dispenser </t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Wash basin</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -1201,35 +1228,35 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="33.65" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="11" t="n">
         <v>1167</v>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">L3 FP Valet office </t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="14" t="n"/>
+      <c r="I3" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1244,5 +1271,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>